--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC I/LTAIPT_A63F01.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES I-X/FRACC I/LTAIPT_A63F01.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="220">
   <si>
     <t>48946</t>
   </si>
@@ -134,493 +134,493 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>F4F3CF1C5B51A9D3CE43B903329E6E20</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos</t>
+  </si>
+  <si>
+    <t>05/02/2017</t>
+  </si>
+  <si>
+    <t>28/05/2021</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/CPEUM.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>06/10/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>F5A64B7524FCEB40AF31C8CAB110A94D</t>
+  </si>
+  <si>
+    <t>Tratado internacional</t>
+  </si>
+  <si>
+    <t>Convención Americana sobre los Derechos del Hombre (Pacto de San José)</t>
+  </si>
+  <si>
+    <t>18/07/1978</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCIONAAMERICANA%20SOBRED.H..pdf</t>
+  </si>
+  <si>
+    <t>72AFDB95F4879C8131F8E38849A2BE3A</t>
+  </si>
+  <si>
+    <t>Pacto internacional de Derechos Civiles y Politicos</t>
+  </si>
+  <si>
+    <t>20/05/1981</t>
+  </si>
+  <si>
+    <t>22/06/1981</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Juridica/PACTO%20INTERNACIONAL%20DE%20DERECHOS%20CIVILES%20Y%20POLITICOS.pdf</t>
+  </si>
+  <si>
+    <t>Subdireccion Juridica</t>
+  </si>
+  <si>
+    <t>3A3CB5816CAA212D73A7C2F084F1F6F3</t>
+  </si>
+  <si>
+    <t>Pacto Internacional de Derechos Economicos Sociales y Culturales</t>
+  </si>
+  <si>
+    <t>03/01/1973</t>
+  </si>
+  <si>
+    <t>03/01/1971</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Juridica/PACTO%20INTERNACIONAL%20DE%20DERECHOS%20ECONOMICOS%20SOCIALES%20Y%20CULTURALES.pdf</t>
+  </si>
+  <si>
+    <t>8E303A8EEDFA694D9D89585D252795D6</t>
+  </si>
+  <si>
+    <t>Convención sobre los Derechos del Niño</t>
+  </si>
+  <si>
+    <t>09/06/1994</t>
+  </si>
+  <si>
+    <t>20/11/1989</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Convenci%c3%b3nsobrederechosdelni%c3%b1o.pdf</t>
+  </si>
+  <si>
+    <t>CF06E8E35DC5F4E3FB203D326C279D64</t>
+  </si>
+  <si>
+    <t>Convención Interamericana para Prevenir, Sancionar y Erradicar la Violencia contra la Mujer (Convención de Belém Do Pará)</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCION%20PARA%20prevenir,sancionar%20y%20erradicar%20violenciamujer.pdf</t>
+  </si>
+  <si>
+    <t>5E6D7A37B2F3DB16DDE00EB1A626F17E</t>
+  </si>
+  <si>
+    <t>Co85-Convenio sobre la Inspección del Trabajo, 1947 (núm. 85)</t>
+  </si>
+  <si>
+    <t>11/07/1947</t>
+  </si>
+  <si>
+    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C085</t>
+  </si>
+  <si>
+    <t>EA20A8A2045866E5DE46964C4786AA62</t>
+  </si>
+  <si>
+    <t>Co-87- Convenio Sobre la Libertad Sindical y la Protección del Derecho de Sindicación, 1948 (núm. 87)</t>
+  </si>
+  <si>
+    <t>09/07/1948</t>
+  </si>
+  <si>
+    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C087</t>
+  </si>
+  <si>
+    <t>5889CC730FAEF56254EDBE1BC102AD91</t>
+  </si>
+  <si>
+    <t>Ley General</t>
+  </si>
+  <si>
+    <t>Ley General de Educación</t>
+  </si>
+  <si>
+    <t>30/09/2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Nueva%20Ley%20General%20de%20Educaci%C3%B3n.pdf</t>
+  </si>
+  <si>
+    <t>18E3FC3B5F4B16C6E4E4339F52AD58B0</t>
+  </si>
+  <si>
+    <t>Ley Federal</t>
+  </si>
+  <si>
+    <t>Ley General para la Carrera de las Maestras y los Maestros</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Gral%20del%20Sistema%20para%20la%20carrera%20de%20las%20maestras%20y%20maestros.pdf</t>
+  </si>
+  <si>
+    <t>617A7AC4D00B0C0115C82FEC44E045AD</t>
+  </si>
+  <si>
+    <t>Ley Federal del Trabajo</t>
+  </si>
+  <si>
+    <t>01/05/1970</t>
+  </si>
+  <si>
+    <t>18/05/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/LeyFederalTrabajo180522.pdf</t>
+  </si>
+  <si>
+    <t>B8B77CA705EF6EE54CE5308886F75916</t>
+  </si>
+  <si>
+    <t>Ley Orgánica</t>
+  </si>
+  <si>
+    <t>Ley Orgánica para la Administración Pública del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>07/04/1948</t>
+  </si>
+  <si>
+    <t>02/06/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/reglamento%20interior%20de%20la%20secretaria%20de%20la%20funcion%20publica%20tlax%20220212.pdf</t>
+  </si>
+  <si>
+    <t>503EF5D73C97450B27B5138BBAF5ABAE</t>
+  </si>
+  <si>
+    <t>Constitución Política de la entidad federativa</t>
+  </si>
+  <si>
+    <t>Constitución Politica del Estado Libre y Soberano de Tlaxcala</t>
+  </si>
+  <si>
+    <t>25/04/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Constitucion_Pol-Tlaxcala250422pdf.pdf</t>
+  </si>
+  <si>
+    <t>E360879B760915FAE336366A3D27D61D</t>
+  </si>
+  <si>
+    <t>Ley Local</t>
+  </si>
+  <si>
+    <t>Ley de Educación para el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>29/11/2000</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_educacion_Tlax310322.pdf</t>
+  </si>
+  <si>
+    <t>15457FA6B1F404F3B234EC92D99DA42B</t>
+  </si>
+  <si>
+    <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>31/12/2017</t>
+  </si>
+  <si>
+    <t>22/12/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_laboral_Serv_Pub_Tlax_y_Mpios221221.pdf</t>
+  </si>
+  <si>
+    <t>DC270B022B7CC7931B913C32B80E1D03</t>
+  </si>
+  <si>
+    <t>Ley Reglamentaria del Artículo 3ro de la Constitución Política de los Estados Unidos Mexicanos, en Materia de Mejora Continua de la Educación</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Reglamentaria%20del%20art.%203%20de%20la%20CPM%20en%20materia%20de%20mejora%20continua%20de%20la%20Educacion.pdf</t>
+  </si>
+  <si>
+    <t>6D9F1A6560740DFFC716324B0F46EBD2</t>
+  </si>
+  <si>
+    <t>Código Civil en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>20/11/1976</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_civil_Tlax240422.pdf</t>
+  </si>
+  <si>
+    <t>C1F970FB24CDECCFB00E3210B7FACD60</t>
+  </si>
+  <si>
+    <t>Código de Procedimientos Civiles vigente en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/11/1980</t>
+  </si>
+  <si>
+    <t>04/09/2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_de_proced_civiles040918.pdf</t>
+  </si>
+  <si>
+    <t>61144A31D87A7BF8D15705694F61459D</t>
+  </si>
+  <si>
+    <t>Código Penal Federal</t>
+  </si>
+  <si>
+    <t>14/08/2031</t>
+  </si>
+  <si>
+    <t>12/11/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-PENAL-FED121121.pdf</t>
+  </si>
+  <si>
+    <t>98AD34EF52162E6CDCFBA7F2F8203AE9</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>05/08/1981</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_que_crea_el_Colegio_de_Bachilleres_del_Estado_de_Tlaxcala.pdf</t>
+  </si>
+  <si>
+    <t>DA8C76C81AFF680291A64ADEC5C02187</t>
+  </si>
+  <si>
+    <t>Código Nacional de Procedimientos Penales</t>
+  </si>
+  <si>
+    <t>05/03/2014</t>
+  </si>
+  <si>
+    <t>09/02/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-NAC-PROCED-PENALES_190221.pdf</t>
+  </si>
+  <si>
+    <t>F087B0F71101AA2A29FC0BA2C53A17BC</t>
+  </si>
+  <si>
+    <t>Código Penal vigente en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>02/01/1980</t>
+  </si>
+  <si>
+    <t>13/09/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_penal_TLAX130921.pdf</t>
+  </si>
+  <si>
+    <t>F34851BDBC105C49D55B8BCB7E9D28FD</t>
+  </si>
+  <si>
+    <t>Ley de las Entidades Paraestatales del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/10/1995</t>
+  </si>
+  <si>
+    <t>12/04/2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_las_entidades_paraestatales_tlax120418.pdf</t>
+  </si>
+  <si>
+    <t>1B69385B98D274E9A271EFCE059D7D70</t>
+  </si>
+  <si>
+    <t>Ley del Procedimiento Administrativo del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>30/11/2001</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_del_procedimiento_Admtvo_Tlax120418.pdf</t>
+  </si>
+  <si>
+    <t>32485152D4FE124834708D2D25A2E2C2</t>
+  </si>
+  <si>
+    <t>Ley de Transparencia y Acceso a la Información Pública del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>22/05/2012</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_transparencia-Tlax_aaceso_inf_pub_tlax1430921.pdf</t>
+  </si>
+  <si>
+    <t>493B23D3B51C085D3148511EA1E9F8DA</t>
+  </si>
+  <si>
+    <t>Ley de Entrega- Recepción para el Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>18/05/2011</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Entrega_Recepcion_para_el_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
+  </si>
+  <si>
+    <t>9F27E038662F6D0C25DDF69032AE953D</t>
+  </si>
+  <si>
+    <t>Ley de Protección de Datos Personales en Posesión de Sujetos Obligados del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>14/05/2012</t>
+  </si>
+  <si>
+    <t>18/07/2017</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/LEY_DE_DATOS.pdf</t>
+  </si>
+  <si>
+    <t>8014B37BD5841386154B98A2526D7653</t>
+  </si>
+  <si>
+    <t>Ley de Archivos del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/05/2011</t>
+  </si>
+  <si>
+    <t>10/05/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_Archivos_Tlaxcala100521.pdf</t>
+  </si>
+  <si>
+    <t>AF564F305DDF7E2F0A708F2DFB841696</t>
+  </si>
+  <si>
+    <t>Ley de Mejora Regulatoria del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>09/05/2013</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Mejora_Regulatoria_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
+  </si>
+  <si>
+    <t>B8E3CCBDE23DBD0939734CC7A0440944</t>
+  </si>
+  <si>
+    <t>Código de Conducta para las y los Servidores Públicos del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>28/04/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/CODIGO%20DE%20CONDUCTA%20COBAT.pdf</t>
+  </si>
+  <si>
+    <t>19285DDE0553E838EE327885B654BA28</t>
+  </si>
+  <si>
+    <t>Código de Ética y Reglas de Integridad para las y los Servidores Públicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>07/07/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/C%C3%93DIGO%20DE%20%C3%89TICA%20Y%20REGLAS%20DE%20INTEGRIDAD%20DE%20COBAT%20PUBLICADO%20EN%20PERI%C3%93DICO%20OFICIAL.pdf</t>
+  </si>
+  <si>
+    <t>734EEF151A47BB868768C766E30061DB</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea al Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>06/02/1985</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/PUBLICACI%c3%93N%20PER.%20OFICIAL%20REGLAMENTO%20INTERIOR%20COBAT.pdf</t>
+  </si>
+  <si>
+    <t>6605C3FFBA1B98C5B3474C5BDBDD4498</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>57639C85C4FE2B8A91947D01B12E027A</t>
+  </si>
+  <si>
+    <t>Reglamento Interior de la Secretaría de la Función Pública</t>
+  </si>
+  <si>
+    <t>22/02/2012</t>
+  </si>
+  <si>
+    <t>Estatuto</t>
+  </si>
+  <si>
+    <t>Ley Reglamentaria</t>
+  </si>
+  <si>
+    <t>Código</t>
   </si>
   <si>
     <t>Reglamento</t>
-  </si>
-  <si>
-    <t>Reglamento Interior de la Secretaria de la Función Pública</t>
-  </si>
-  <si>
-    <t>22/02/2012</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/reglamento%20interior%20de%20la%20secretaria%20de%20la%20funcion%20publica%20tlax%20220212.pdf</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea El Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>06/02/1985</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/PUBLICACI%c3%93N%20PER.%20OFICIAL%20REGLAMENTO%20INTERIOR%20COBAT.pdf</t>
-  </si>
-  <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>28/04/2021</t>
-  </si>
-  <si>
-    <t>Código</t>
-  </si>
-  <si>
-    <t>Código de Conducta para las y los Servidores Públicos del organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/CODIGO%20DE%20CONDUCTA%20COBAT.pdf</t>
-  </si>
-  <si>
-    <t>Código Penal vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>02/01/1980</t>
-  </si>
-  <si>
-    <t>13/09/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_penal_TLAX130921.pdf</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Código de Ética y Reglas de Integridad para las y los Servidores Públicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>07/07/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/C%C3%93DIGO%20DE%20%C3%89TICA%20Y%20REGLAS%20DE%20INTEGRIDAD%20DE%20COBAT%20PUBLICADO%20EN%20PERI%C3%93DICO%20OFICIAL.pdf</t>
-  </si>
-  <si>
-    <t>Ley Local</t>
-  </si>
-  <si>
-    <t>Ley de Mejora Regulatoria del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>09/05/2013</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Mejora_Regulatoria_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Archivos del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/05/2011</t>
-  </si>
-  <si>
-    <t>10/05/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_Archivos_Tlaxcala100521.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Protección de Datos Personales para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>14/05/2012</t>
-  </si>
-  <si>
-    <t>18/07/2017</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/LEY_DE_DATOS.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Entrega-Recepción para el Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>18/05/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Entrega_Recepcion_para_el_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>22/05/2012</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_transparencia-Tlax_aaceso_inf_pub_tlax1430921.pdf</t>
-  </si>
-  <si>
-    <t>Ley del Procedimiento Administrativo del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>30/11/2001</t>
-  </si>
-  <si>
-    <t>12/04/2018</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_del_procedimiento_Admtvo_Tlax120418.pdf</t>
-  </si>
-  <si>
-    <t>Ley de las Entidades Paraestatales para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/10/1995</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_las_entidades_paraestatales_tlax120418.pdf</t>
-  </si>
-  <si>
-    <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>31/12/2017</t>
-  </si>
-  <si>
-    <t>22/12/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_laboral_Serv_Pub_Tlax_y_Mpios221221.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Educación para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>29/11/2000</t>
-  </si>
-  <si>
-    <t>31/03/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_educacion_Tlax310322.pdf</t>
-  </si>
-  <si>
-    <t>Código Nacional de Procedimientos Penales</t>
-  </si>
-  <si>
-    <t>05/03/2014</t>
-  </si>
-  <si>
-    <t>19/02/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-NAC-PROCED-PENALES_190221.pdf</t>
-  </si>
-  <si>
-    <t>Código Penal Federal</t>
-  </si>
-  <si>
-    <t>14/08/2031</t>
-  </si>
-  <si>
-    <t>12/11/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-PENAL-FED121121.pdf</t>
-  </si>
-  <si>
-    <t>Código de Procedimientos Civiles vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/11/1980</t>
-  </si>
-  <si>
-    <t>04/09/2018</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_de_proced_civiles040918.pdf</t>
-  </si>
-  <si>
-    <t>Código Civil vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>20/11/1976</t>
-  </si>
-  <si>
-    <t>25/04/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_civil_Tlax240422.pdf</t>
-  </si>
-  <si>
-    <t>Ley Reglamentaria</t>
-  </si>
-  <si>
-    <t>Ley Reglamentaria del Artículo 3o. de la Constitución Política de los Estados Unidos Mexicanos,  en materia de Mejora Continua de la Educación</t>
-  </si>
-  <si>
-    <t>30/09/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Reglamentaria%20del%20art.%203%20de%20la%20CPM%20en%20materia%20de%20mejora%20continua%20de%20la%20Educacion.pdf</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>05/08/1981</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_que_crea_el_Colegio_de_Bachilleres_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley Orgánica</t>
-  </si>
-  <si>
-    <t>Ley Orgánica de la Administración Pública del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>07/04/1998</t>
-  </si>
-  <si>
-    <t>02/06/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_Organica_de_Admcion_Pub20622.pdf</t>
-  </si>
-  <si>
-    <t>Tratado internacional</t>
-  </si>
-  <si>
-    <t>C087 - Convenio sobre la libertad sindical y la protección del derecho de sindicación, 1948 (núm. 87)</t>
-  </si>
-  <si>
-    <t>09/07/1948</t>
-  </si>
-  <si>
-    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C087</t>
-  </si>
-  <si>
-    <t>El Colegio de Bachilleres del Estado de Tlaxcala manifiesta a través de la Unidad Admnistrativa Subdireccióm Jurídica que este documento al ser un acuerdo celebrado y un pacto de voluntades entre varios Países a nivel internacional, no es sujeto de reforma.</t>
-  </si>
-  <si>
-    <t>C085 - Convenio sobre la inspección del trabajo (territorios no metropolitanos), 1947 (núm. 85)</t>
-  </si>
-  <si>
-    <t>11/07/1947</t>
-  </si>
-  <si>
-    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C085</t>
-  </si>
-  <si>
-    <t>Convención Interamericana para Prevenir, Sancionar y Erradicar la Violencia Contra la Mujer</t>
-  </si>
-  <si>
-    <t>09/06/1994</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCION%20PARA%20prevenir,sancionar%20y%20erradicar%20violenciamujer.pdf</t>
-  </si>
-  <si>
-    <t>Convención sobre los Derechos del Niño</t>
-  </si>
-  <si>
-    <t>20/11/1989</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Convenci%c3%b3nsobrederechosdelni%c3%b1o.pdf</t>
-  </si>
-  <si>
-    <t>Convención Americana sobre Derechos Humanos (Pacto de San José)</t>
-  </si>
-  <si>
-    <t>18/07/1978</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCIONAAMERICANA%20SOBRED.H..pdf</t>
-  </si>
-  <si>
-    <t>Ley General</t>
-  </si>
-  <si>
-    <t>Ley General de Educación</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Nueva%20Ley%20General%20de%20Educaci%C3%B3n.pdf</t>
-  </si>
-  <si>
-    <t>Ley General del Sistema para la Carrera de las Maestras y los Maestros</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Gral%20del%20Sistema%20para%20la%20carrera%20de%20las%20maestras%20y%20maestros.pdf</t>
-  </si>
-  <si>
-    <t>Constitución Política de la entidad federativa</t>
-  </si>
-  <si>
-    <t>Constitución Política del Estado Libre y Soberano de Tlaxcala</t>
-  </si>
-  <si>
-    <t>05/02/2017</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Constitucion_Pol-Tlaxcala250422pdf.pdf</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos</t>
-  </si>
-  <si>
-    <t>28/05/2021</t>
-  </si>
-  <si>
-    <t>Ley Federal</t>
-  </si>
-  <si>
-    <t>Ley Federal del Trabajo</t>
-  </si>
-  <si>
-    <t>01/05/1970</t>
-  </si>
-  <si>
-    <t>18/05/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/LeyFederalTrabajo180522.pdf</t>
-  </si>
-  <si>
-    <t>527A9743322EAB76D7745BA195131921</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>04/07/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de  julio de 2022 al 30 de septiembre  de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública del Reglamento Interior de la Secretaria de la Función Pública, el cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>01D305DC6B7657B1D00A2E6158D37253</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de  julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública del Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala, el cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>B2B816438E2B2ED322E3560FE977A534</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de  julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública del Reglamento General de la Ley que Crea El Colegio de Bachilleres del Estado de Tlaxcala el cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>6DEF214B4BD967DFE800E1E7A97C531A</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de  julio de 2022 al 30 de septiembre  de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública del Código de  Ética y Reglas de Integridad para las y los Servidores Públicos del Colegio de Bachilleres del Estado de Tlaxcala, el cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>206BE74982D48D8EE40FBA6AB3C2BECA</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de  julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública del  Código de Conducta para las y los Servidores Públicos del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala, el cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>1D7F6D3375D1629F6747319C37331E6A</t>
-  </si>
-  <si>
-    <t>B6A8AB1B99104322C09EEDBE82BEF9A0</t>
-  </si>
-  <si>
-    <t>A4B829585E10C5BB82CA99B92554B94C</t>
-  </si>
-  <si>
-    <t>EC4DDF42704B6FCF4266A3004C482C78</t>
-  </si>
-  <si>
-    <t>4E161F60092867EBFCB47B26272820D1</t>
-  </si>
-  <si>
-    <t>74F4C72073B4F2E620C3B6A50232EF75</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública de la Ley Reglamentaria del Artículo 3o. de la Constitución Política de los Estados Unidos Mexicanos,  en materia de Mejora Continua de la Educación, la cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>2C5504E4EAF18F9A055A069529DC5477</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de  julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala, la cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>33C3057207EC6D4F60EF74BEF0B9F603</t>
-  </si>
-  <si>
-    <t>5D1026455319F7BA8DF0FE1757ED8B49</t>
-  </si>
-  <si>
-    <t>51EC2C98BC87400A8E54A91DF0A7931D</t>
-  </si>
-  <si>
-    <t>7D2818E24148256C6317BAA991FBD1E9</t>
-  </si>
-  <si>
-    <t>7EC2951BF2BB3F418A8346DD612B4582</t>
-  </si>
-  <si>
-    <t>3749B079A62991B742B4B7F21FA4F4B4</t>
-  </si>
-  <si>
-    <t>D85B74A16E42727AAED4B6A8B9538F19</t>
-  </si>
-  <si>
-    <t>74F78CB7A17537875F433C5AC393CDFD</t>
-  </si>
-  <si>
-    <t>513E6D90D0C0471DE9F4B529DAFCA1B6</t>
-  </si>
-  <si>
-    <t>0EB9F58F6E7A074B742C5A694E7995F8</t>
-  </si>
-  <si>
-    <t>215E892FF93583A132BBC4BA1A25C315</t>
-  </si>
-  <si>
-    <t>B015DB5F2149DA8D162102A65FB840E6</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública de la Ley General del Sistema para la Carrera de las Maestras y los Maestros, la cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>5E6B7D6FC9F4764D77195C2508EA39CD</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública de la Ley General de Educación, la cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>B5E50A522095E8B62F4A00641CAA47F6</t>
-  </si>
-  <si>
-    <t>89C1D0F3CA0E386337C36947A7066CD6</t>
-  </si>
-  <si>
-    <t>4EE47EBA695D160AA2CCDDED977CC024</t>
-  </si>
-  <si>
-    <t>D0DCF32BFFC8977D38D8EEC68385B577</t>
-  </si>
-  <si>
-    <t>4D707AE776EF52564CC5EEF3CB99C76A</t>
-  </si>
-  <si>
-    <t>9783AD55F703256538039FB3987B6D18</t>
-  </si>
-  <si>
-    <t>FBA27C83FD5767D6C4B3435B068E0F8B</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Const.%20Fedral%2028-mayo-21.pdf</t>
-  </si>
-  <si>
-    <t>Estatuto</t>
   </si>
   <si>
     <t>Decreto</t>
@@ -1070,22 +1070,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="121" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="242.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="255" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -1258,921 +1258,921 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>158</v>
+        <v>52</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>161</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>167</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>174</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="M20" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>150</v>
@@ -2187,385 +2187,467 @@
         <v>153</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>189</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2661,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E169">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -2594,57 +2676,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
